--- a/SeleniumTests/TestDataFolder/SettingTestDataValid.xlsx
+++ b/SeleniumTests/TestDataFolder/SettingTestDataValid.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\e-invoice\SeleniumTests\TestDataFolder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2E8A55D-37A0-4F70-B5A0-E1349186C125}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E444E48-3BB7-43CD-9A52-9269D75FB1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="33900" yWindow="3420" windowWidth="13830" windowHeight="7965" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CreateNewSettingTestData" sheetId="3" r:id="rId1"/>
@@ -52,27 +52,12 @@
     <t>true</t>
   </si>
   <si>
-    <t>CutOffDateReset</t>
-  </si>
-  <si>
-    <t>ConsolidateCutOffDateReset</t>
-  </si>
-  <si>
-    <t>SecurityTokenReset</t>
-  </si>
-  <si>
     <t>false</t>
   </si>
   <si>
-    <t>Entity Name</t>
-  </si>
-  <si>
     <t>Store Name</t>
   </si>
   <si>
-    <t>MR D.I.Y. KIDS SDN. BHD.: Store 2</t>
-  </si>
-  <si>
     <t>View (compact/comfortable)</t>
   </si>
   <si>
@@ -80,6 +65,21 @@
   </si>
   <si>
     <t>comfortable</t>
+  </si>
+  <si>
+    <t>B2C Cut Off Date Reset</t>
+  </si>
+  <si>
+    <t>Auto Consolidate Cut Off Date Reset</t>
+  </si>
+  <si>
+    <t>Security Token Reset</t>
+  </si>
+  <si>
+    <t>Business Entity Name</t>
+  </si>
+  <si>
+    <t>QUBE APPS MARKETING SDN. BHD.: Store 2</t>
   </si>
 </sst>
 </file>
@@ -412,7 +412,7 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -426,7 +426,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -438,19 +438,25 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6538E9C9-4BFC-4A2D-813B-2C124F087332}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" t="s">
         <v>6</v>
-      </c>
-      <c r="D1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -461,10 +467,10 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -476,18 +482,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D1CC3AF-65FD-422C-B2A6-706339CCEA36}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
